--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0107.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0107.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Không thể phá hủy thực thể triệu hồi</t>
+          <t>Không thể tiêu diệt thực thể triệu hồi</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Bạn đã bị loại khỏi nhóm</t>
+          <t>Bạn đã bị loại khỏi nhóm.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Một người chơi không thể tham gia Chế độ Co-op</t>
+          <t>Người chơi không thể tham gia Chế Độ Hợp Tác.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Bạn không thể tham gia Chế độ Co-op</t>
+          <t>Cậu không thể tham gia Chế Độ Hợp Tác</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Yêu cầu kết bạn mới</t>
+          <t>Yêu Cầu Kết Bạn Mới</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Thử lại</t>
+          <t>Thử Lại</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Switch Operation Mode</t>
+          <t>Chuyển Chế Độ Hoạt Động</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Tài khoản của bạn tạm thời bị hạn chế sử dụng chức năng xã hội</t>
+          <t>Tài khoản của cậu tạm thời bị hạn chế sử dụng các chức năng xã hội</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Proceed</t>
+          <t>Tiến lên</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Not Now</t>
+          <t>Không phải lúc này</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Rate Now</t>
+          <t>Đánh giá ngay</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Không có sự kiện khả dụng</t>
+          <t>Không có sự kiện nào khả dụng</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Immersion Mode</t>
+          <t>Chế độ Hòa Nhập</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Trang Bị Hình Ảnh Vũ Khí</t>
+          <t>Trang bị Chiếu Vũ Khí</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Echo Challenge: Plushie Punch</t>
+          <t>Thử Thách Tiếng Vọng: Đấm Bông Nhồi Bông</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Đội đã bị giải tán</t>
+          <t>Nhóm đã bị giải tán.</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Sự kiện không khả dụng</t>
+          <t>Sự kiện chưa khả dụng</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Lỗi không xác định</t>
+          <t>Lỗi Không Xác Định</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Vật phẩm này không thể loại bỏ</t>
+          <t>Vật phẩm này không thể vứt bỏ.</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Vật phẩm này không thể loại bỏ</t>
+          <t>Vật phẩm này không thể vứt bỏ.</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Vượt quá số lượng tối đa cho Gộp Hàng loạt</t>
+          <t>Đã vượt quá số lượng tối đa cho Tinh Luyện Hàng Loạt</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Echo đã tồn tại</t>
+          <t>Đã sở hữu Echo này rồi</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Không thể thêm Echo không thường</t>
+          <t>Không thể thêm Echo bất thường</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Đang trực tuyến</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Tìm kiếm theo UID để thêm bạn</t>
+          <t>Tìm theo UID để thêm bạn</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Tìm bạn bằng Online ID cho PSN™</t>
+          <t>Tìm theo Online ID trên PSN™ để thêm bạn</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Tìm kiếm bằng Online ID cho PSN</t>
+          <t>Tìm theo Online ID trên PSN</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Bạn đã yêu cầu cài đặt đầu vào quá thường xuyên</t>
+          <t>Ngươi đã yêu cầu cài đặt đầu vào quá nhiều lần.</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Bạn đã yêu cầu cài đặt đầu vào quá thường xuyên</t>
+          <t>Ngươi đã yêu cầu cài đặt đầu vào quá nhiều lần.</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Bạn đã yêu cầu cài đặt đầu vào quá thường xuyên</t>
+          <t>Ngươi đã yêu cầu cài đặt đầu vào quá nhiều lần.</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Bạn đã yêu cầu cài đặt đầu vào quá thường xuyên</t>
+          <t>Ngươi đã yêu cầu cài đặt đầu vào quá nhiều lần.</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Không tìm thấy thao tác cài đặt đầu vào</t>
+          <t>Thao tác cài đặt đầu vào không tìm thấy</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Không tìm thấy thao tác cài đặt đầu vào</t>
+          <t>Thao tác cài đặt đầu vào không tìm thấy</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Không tìm thấy thao tác cài đặt đầu vào</t>
+          <t>Thao tác cài đặt đầu vào không tìm thấy</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Không tìm thấy thao tác cài đặt đầu vào</t>
+          <t>Thao tác cài đặt đầu vào không tìm thấy</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Đã cấu hình quá nhiều phím trong cài đặt đầu vào</t>
+          <t>Đã cấu hình quá nhiều phím</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Đã cấu hình quá nhiều phím trong cài đặt đầu vào</t>
+          <t>Đã cấu hình quá nhiều phím</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Đã cấu hình quá nhiều phím trong cài đặt đầu vào</t>
+          <t>Đã cấu hình quá nhiều phím</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Đã cấu hình quá nhiều phím trong cài đặt đầu vào</t>
+          <t>Đã cấu hình quá nhiều phím</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Đã cấu hình quá nhiều phím trong cài đặt đầu vào</t>
+          <t>Đã cấu hình quá nhiều phím</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Đã cấu hình quá nhiều phím trong cài đặt đầu vào</t>
+          <t>Đã cấu hình quá nhiều phím</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Tên loại phụ thiết bị cài đặt đầu vào quá dài</t>
+          <t>Tên loại thiết bị cài đặt đầu vào quá dài</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Lấy mã xác minh</t>
+          <t>Lấy mã xác nhận</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Thông tin người dùng không tìm thấy</t>
+          <t>Không tìm thấy thông tin người dùng</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 15</t>
+          <t>Đạt Cấp Độ Liên Minh 15</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "Kiếm Kích Băng Hoang"</t>
+          <t>Hoàn thành Nhiệm Vụ Chính "Clashing Blades"</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương Nhiệm Vụ Chính VII "Thời Khắc Tan Băng" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Chính Chương VII "Thaw of Eons" để mở khóa</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Official Community "KURO APP"</t>
+          <t>Ứng Dụng Cộng Đồng Chính Thức "KURO APP"</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Phần thưởng Liên Kết Email</t>
+          <t>Phần Thưởng Liên Kết Email</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Phần thưởng Liên Kết Email</t>
+          <t>Phần Thưởng Liên Kết Email</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Proceed</t>
+          <t>Tiến lên</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Liên kết Email</t>
+          <t>Email Liên Kết</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>Hoàn tất</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Email Linked</t>
+          <t>Email Đã Liên Kết</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Switch Weapon Projection</t>
+          <t>Chuyển Dự Án Vũ Khí</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Nhận Phần Thưởng</t>
+          <t>Nhận thưởng</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Nhân đôi</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Bổ Sung</t>
+          <t>Phụ</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Add Tất cả</t>
+          <t>Thêm Tất Cả</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Thêm theo Bước</t>
+          <t>Thêm Theo Bước</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và hoàn thành Nhiệm Vụ Chính: Chương I Chương VIII "Đến Bờ Biển Cuối Cùng"</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và hoàn thành Nhiệm Vụ Chính: Chương I Hồi VIII "Đến Bờ Biển Cuối Cùng"</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính: Đến Bờ Biển Cuối Cùng</t>
+          <t>Hoàn thành Nhiệm Vụ Chính: Tới Bờ Cát Cuối Cùng</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14</t>
+          <t>Đạt Cấp Độ Liên Minh 14</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Người chơi bạn mời đã bị đánh bại và không thể tham gia Chơi Cùng Nhau</t>
+          <t>Người chơi bạn mời đã bị đánh bại và không thể tham gia Chơi Cùng</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Số lần Nhận Thưởng được đặt lại vào mỗi thứ Hai</t>
+          <t>Số lần nhận thưởng sẽ được reset vào mỗi thứ Hai</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi vượt qua độ khó trước đó</t>
+          <t>Mở khóa sau khi hoàn thành Độ Khó trước đó</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Trang phục Switched</t>
+          <t>Đã Thay Đổi Trang Phục</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Hoàn thành Giấc Mộng Kỳ Diệu: Ngọn Núi và Sáu Tín Dụng</t>
+          <t>Hoàn thành Hành Trình Giấc Mơ: Ngọn Núi và Sáu Đồng Tín Dụng</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Hoàn thành Giấc Mộng Kỳ Diệu: Sân Khấu Chiến Binh Nhỏ</t>
+          <t>Hoàn thành Hành Trình Giấc Mơ: Sân Khấu Của Chiến Binh Nhí</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Complete Dreamscape Odyssey: Neverending Inferno</t>
+          <t>Hoàn thành Hành Trình Giấc Mơ: Hỏa Ngục Bất Tận</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Hoàn thành Giấc Mộng Kỳ Diệu: Nghiên Cứu Trong Tuyết</t>
+          <t>Hoàn thành Hành Trình Giấc Mơ: Nghiên Cứu Tuyết Rơi</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Complete Dreamscape Odyssey: Blooming Reverie</t>
+          <t>Hoàn thành Hành Trình Giấc Mơ: Khúc Hoài Niệm Nở Hoa</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Hoàn thành "Khi Đêm Gõ Cửa"</t>
+          <t>Hoàn thành "Khi Bóng Đêm Gõ Cửa".</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Chiến Binh Mưu Kế Kẹp Đòn</t>
+          <t>Chiến Binh Mưu Kế Kẹp Nã</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Chi tiết Giai đoạn</t>
+          <t>Chi Tiết Giai Đoạn</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Chọn Buff</t>
+          <t>Chọn Buffs</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình giai đoạn Chiến Binh Mũi Kẹp</t>
+          <t>Không tìm thấy cấu hình giai đoạn cho Chiến Binh Mũi Kìm.</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Chiến Binh Mũi Kẹp hiện không khả dụng</t>
+          <t>Chiến Binh Mũi Kìm hiện không khả dụng.</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Hiện không ở nửa đầu của giai đoạn</t>
+          <t>Hiện chưa vào được nửa đầu của màn chơi</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Insufficient Points</t>
+          <t>Điểm không đủ</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Hiện không ở giai đoạn Chiến Binh Mũi Kẹp</t>
+          <t>Hiện không ở trong giai đoạn Chiến Binh Kẹp Đối Đầu</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Sự kiện đã kết thúc</t>
+          <t>Sự kiện đã hết hạn</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Chưa triển khai Resonator nào</t>
+          <t>Chưa triển khai Resonator</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 40</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 40</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Hoàn thành "When the Night Knocks" để mở khóa</t>
+          <t>Tiến hành "Khi Đêm Gõ Cửa" để mở khóa</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Bạn đã nhận thưởng sự kiện rồi</t>
+          <t>Ngươi đã nhận phần thưởng sự kiện rồi</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Chức năng Chỉnh Sửa Dữ Liệu chưa được kích hoạt</t>
+          <t>Chức năng Điều Chỉnh Dữ Liệu chưa được kích hoạt</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Đã chọn thuộc tính trùng lặp</t>
+          <t>Thuộc tính đã chọn trùng lặp</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Discarded Vật phẩm</t>
+          <t>Vật Phẩm Bị Loại Bỏ</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương I Hồi III "Ominous Star" của Nhiệm Vụ Chính để mở khóa</t>
+          <t>Hoàn thành Chương III "Ngôi Sao Điềm Gở" của Chương I Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Conversion</t>
+          <t>Chuyển hóa</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 20 và hoàn thành "What Yesterday Wept, Hôm nay Doth Sing" để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 20 và hoàn thành "Điều Hôm Qua Khóc, Hôm Nay Hát" để mở khóa</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương II Hồi III "What Yesterday Wept, Hôm nay Doth Sing" của Nhiệm Vụ Chính</t>
+          <t>Hoàn thành Chương II Hồi III "Điều Hôm Qua Khóc, Hôm Nay Hát" của Nhiệm Vụ Chính</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 20</t>
+          <t>Đạt Cấp Độ Liên Minh 20</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Phần thưởng gameplay</t>
+          <t>Phần Thưởng Gameplay</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Hướng Dẫn "Dream Patrol I" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Hướng Dẫn "Tuần Tra Giấc Mơ I" để mở khóa</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Khám phá tất cả thử thách Dream Patrol ở Penitent's End để mở khóa</t>
+          <t>Hoàn thành tất cả thử thách Tuần Tra Giấc Mơ tại Penitent's End để mở khóa</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Hướng Dẫn "Dream Patrol I" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Hướng Dẫn "Tuần Tra Giấc Mơ I" để mở khóa</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Hướng Dẫn "Dream Patrol I" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Hướng Dẫn "Tuần Tra Giấc Mơ I" để mở khóa</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Hướng Dẫn "Dream Patrol I" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Hướng Dẫn "Tuần Tra Giấc Mơ I" để mở khóa</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả thử thách Dream Patrol tại Bán đảo Fagaceae để mở khóa</t>
+          <t>Hoàn thành tất cả thử thách Tuần Tra Giấc Mơ tại Bán Đảo Fagaceae để mở khóa</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Hướng Dẫn "Dream Patrol I" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Hướng Dẫn "Tuần Tra Giấc Mơ I" để mở khóa</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả thử thách Ruins Where Shadows Roam tại Penitent's End để mở khóa</t>
+          <t>Hoàn thành tất cả thử thách Tàn Tích Nơi Bóng Tối Lang Thang tại Penitent's End để mở khóa.</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Synthesize</t>
+          <t>Tổng hợp</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Vui lòng sử dụng vật liệu Chuyển đổi cần thiết</t>
+          <t>Hãy sử dụng vật liệu Chuyển hóa cần thiết</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Không thể thực hiện hành động này ở trạng thái hiện tại</t>
+          <t>Hiện không thể thực hiện hành động này</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "Through the Sea Thou Break" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Chính "Vượt Qua Biển Cả" để mở khóa</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "Through the Sea Thou Break" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Chính "Vượt Qua Biển Cả" để mở khóa</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "Through the Sea Thou Break" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Chính "Vượt Qua Biển Cả" để mở khóa</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Nhạc hiện tại đã được đặt làm Nhạc Nền</t>
+          <t>Đã đặt bản nhạc hiện tại làm Nhạc Nền</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Set As Background Music</t>
+          <t>Đặt làm nhạc nền</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Set As Background Music</t>
+          <t>Đặt làm nhạc nền</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Đã hủy cài đặt Nhạc Nền</t>
+          <t>Đã hủy cài đặt nhạc nền</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 25 để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 25 để mở khóa</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 35 để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 35 để mở khóa</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 22 và tiến đến Chương II Hồi I Nhiệm Vụ Chính để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 22 và tiến đến Chương II Hồi I Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14</t>
+          <t>Đạt Cấp Độ Liên Minh 14</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 để mở khóa trong Chương II Hồi I Nhiệm Vụ Chính</t>
+          <t>Đạt Cấp Độ Liên Minh 14 để mở khóa trong Chương II Hồi I của Nhiệm Vụ Chính</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 22 và mở khóa Chế Độ Hợp Tác</t>
+          <t>Đạt Cấp Độ Liên Minh 22 và mở khóa Chế Độ Hợp Tác</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 27</t>
+          <t>Đạt Cấp Độ Liên Minh 27</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Abandon</t>
+          <t>Bỏ mặc</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Cần khởi động lại game để thay đổi có hiệu lực</t>
+          <t>Cần khởi động lại trò chơi để thay đổi có hiệu lực</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Sự kiện này đã kết thúc</t>
+          <t>Sự kiện đã chấm dứt</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Quay lại</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Mở khóa "Wonder Bubble"</t>
+          <t>Mở khóa "Bong Bóng Kỳ Diệu"</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Disembark</t>
+          <t>Xuống tàu</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Vòng biển đã được làm mới</t>
+          <t>Chu kỳ biển đã được làm mới.</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Sử dụng Mồi</t>
+          <t>Dùng Mồi</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Sử dụng Mồi</t>
+          <t>Dùng Mồi</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Di chuyển nhanh đến Bến tàu</t>
+          <t>Dịch chuyển Nhanh đến Bến tàu</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Kiểm tra Yêu cầu</t>
+          <t>Kiểm tra Yêu Cầu</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên minh 22 để mở khóa Chế độ Hợp tác</t>
+          <t>Đạt Cấp Độ Liên Minh 22 và mở khóa Chế Độ Hợp Tác</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên minh 22 và mở khóa Tiện ích: Bay để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 22 và mở khóa Tiện Ích: Bay để mở khóa</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Refresh Request</t>
+          <t>Yêu cầu làm mới</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Nhận được thông qua Câu cá (tỷ lệ thấp)</t>
+          <t>Có thể thu được qua Câu Cá (tỷ lệ thấp)</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Nhận được thông qua Bong bóng Kỳ diệu</t>
+          <t>Có thể thu được qua Bong Bóng Kỳ Diệu</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Mở khóa thông qua tiến trình câu chuyện hoặc mục Index</t>
+          <t>Mở khóa thông qua tiến trình câu chuyện hoặc mục trong Chỉ Mục</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Night Fishing</t>
+          <t>Câu Cá Đêm</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Night Fishing</t>
+          <t>Câu Cá Đêm</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Vùng Đất Than Khóc chưa được bắt đầu</t>
+          <t>Vùng Đất Than Khóc chưa bắt đầu</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Thử thách thất bại</t>
+          <t>Thử thách Thất bại</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Chỉ chủ phòng mới có thể ghép trận trong Chế độ Hợp tác nhiều người chơi</t>
+          <t>Chỉ chủ phòng mới có thể ghép trận trong Chế độ Hợp Tác Đa Người Chơi</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Đã nhận phần thưởng</t>
+          <t>Đã nhận phần thưởng rồi</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Tất cả đội phải mang theo Token</t>
+          <t>Mọi đội phải mang theo một Token.</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Tất cả đội phải mang theo Token</t>
+          <t>Mọi đội phải mang theo một Token.</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Không đủ lần sử dụng Token</t>
+          <t>Số lần sử dụng Token không đủ.</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Không đủ lần sử dụng Token</t>
+          <t>Số lần sử dụng Token không đủ.</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Chỉnh sửa dữ liệu</t>
+          <t>Điều Chỉnh Dữ Liệu</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Xác nhận Hủy bỏ</t>
+          <t>Xác nhận Phá hủy</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>ID sự kiện không khớp</t>
+          <t>ID Sự kiện không khớp</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Tính toán phần thưởng sự kiện thất bại</t>
+          <t>Không thể tính toán phần thưởng sự kiện</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Insufficient Dream Fragments</t>
+          <t>Mảnh Giấc Mơ không đủ</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Mở khóa chức năng Sự kiện</t>
+          <t>Mở khóa chức năng Sự Kiện</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 30</t>
+          <t>Đạt Cấp Độ Liên Minh 30</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 30</t>
+          <t>Đạt Cấp Độ Liên Minh 30</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Cần đội hình đủ 3 người chơi để bắt đầu cuộc đua</t>
+          <t>Cần đủ một đội 3 người chơi để bắt đầu cuộc đua</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Pre-download Resources</t>
+          <t>Tải trước tài nguyên</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Download</t>
+          <t>Tải Xuống</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Mở khóa khi đạt Cấp Liên Minh 30</t>
+          <t>Đạt Cấp Độ Liên Minh 30 để mở khóa</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương II Lời mở đầu Nhiệm vụ Chính để mở khóa</t>
+          <t>Hoàn thành Lời Mở Đầu Chương II trong Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 để mở khóa</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và hoàn thành Chương II Lời mở đầu để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và hoàn thành Lời Mở Đầu Chương II để mở khóa</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 để mở khóa</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và hoàn thành Chương II Lời mở đầu Nhiệm vụ Chính để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và hoàn thành Lời Mở Đầu Chương II trong Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Cần đội hình đủ 3 người chơi để bắt đầu cuộc đua</t>
+          <t>Cần đủ đội 3 người chơi để bắt đầu cuộc đua.</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Insufficient Riccioli Fishery Coins</t>
+          <t>Xu Công ty Riccioli Fishery không đủ</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Insufficient Riccioli Fishery Coins</t>
+          <t>Xu Công ty Riccioli Fishery không đủ</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Kỹ Năng Câu Cá bị khóa</t>
+          <t>Kỹ Năng Câu Cá Bị Khóa</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Mái che bị khóa</t>
+          <t>Mái che đã khóa</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Insufficient "Sweet Puff"</t>
+          <t>Không đủ "Bánh Ngọt Xốp"</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Đọc dữ liệu "Chanty Bounty" thất bại</t>
+          <t>Không đọc được dữ liệu "Chanty Bounty"</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Kỹ Năng Câu Cá bị khóa</t>
+          <t>Kỹ Năng Câu Cá Bị Khóa</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Khả năng Câu Cá cần thiết cho Điểm Câu Cá này đang bị khóa</t>
+          <t>Kỹ năng Câu Cá cần thiết cho Điểm Câu Cá này đang bị khóa.</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Lỗi số lượng vật phẩm</t>
+          <t>Số lượng vật phẩm lỗi</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Lỗi số lượng vật phẩm</t>
+          <t>Số lượng vật phẩm lỗi</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Giai đoạn bị khóa</t>
+          <t>Sân khấu bị khóa.</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Hoàn thành mục tiêu Nhiệm vụ Chính "Đặt Hognis lên bệ" để mở khóa</t>
+          <t>Hoàn thành mục tiêu Nhiệm Vụ Chính "Đặt Hognis lên bệ" để mở khóa</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Chính "Thiếu Nữ, Kẻ Nổi Loạn, Kẻ Rao Tin Tử Thần" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Chính "Thiếu Nữ, Kẻ Nổi Loạn, Người Rao Tử Thần" để mở khóa</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Đến Avinoleum trong Nhiệm vụ Chính "Thiếu Nữ, Kẻ Nổi Loạn, Kẻ Rao Tin Tử Thần" để mở khóa</t>
+          <t>Đến Avinoleum trong Nhiệm Vụ Chính "Thiếu Nữ, Kẻ Nổi Loạn, Kẻ Rao Tin Tử Thần" để mở khóa</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Thoát ngay?</t>
+          <t>Thoát Ngay?</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Switch Successful</t>
+          <t>Chuyển Thành Công</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương II Lời Mở Đầu Nhiệm vụ Chính để mở khóa</t>
+          <t>Hoàn thành Lời Mở Đầu Chương II trong Nhiệm Vụ Chính để mở khóa</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Đạt Cấp Độ Liên Minh 14 và hoàn thành Chương II Lời Mở Đầu để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và hoàn thành Lời Mở Đầu Chương II để mở khóa</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Hiện tại bạn không thể sử dụng chức năng này</t>
+          <t>Hiện tại bạn không thể sử dụng chức năng này.</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Đặt lại số lần thử Hỗ Trợ Mô-đun</t>
+          <t>Thử Lại Mô-đun Hỗ Trợ</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Cubie Derby</t>
+          <t>Đua Cubie</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Cubie Derby</t>
+          <t>Đua Cubie</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Cubie Derby</t>
+          <t>Đua Cubie</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương II Hồi III "What Yesterday Wept, Hôm nay Doth Sing" Nhiệm Vụ Chính</t>
+          <t>Hoàn thành Chương II Hồi III "Điều Hôm Qua Khóc, Hôm Nay Hát" của Nhiệm Vụ Chính</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 20 để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 20 để mở khóa</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 20 và hoàn thành "What Yesterday Wept, Hôm nay Doth Sing" để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 20 và hoàn thành "Điều Hôm Qua Khóc, Hôm Nay Hát" để mở khóa</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Downloading</t>
+          <t>Đang tải xuống</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Pausing</t>
+          <t>Đang tạm dừng</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Download</t>
+          <t>Tải Xuống</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Tạm dừng</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Điểm Di chuyển nhanh chưa được mở khóa</t>
+          <t>Điểm dịch chuyển Nhanh chưa được mở khóa</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Bạn không thể mua gói này</t>
+          <t>Bạn không thể mua gói này.</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Quyền truy cập gói này của bạn đã hết hạn</t>
+          <t>Gói ưu đãi của cậu đã hết hạn rồi</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Không phải gói cá nhân</t>
+          <t>Không phải gói cá nhân đâu</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Bạn có quyền truy cập gói này</t>
+          <t>Cậu có quyền truy cập gói này</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Hệ thống Danh Hiệu không khả dụng</t>
+          <t>Hệ thống Danh Hiệu hiện không khả dụng</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>ID Sự Kiện và ID Mùa không khớp</t>
+          <t>ID Sự kiện và ID Mùa không khớp</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Lỗi dữ liệu Nhiệm Vụ Sự Kiện</t>
+          <t>Lỗi dữ liệu sự kiện</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Không tìm thấy ID Nhiệm Vụ</t>
+          <t>Không tìm thấy ID nhiệm vụ</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Đã nhận phần thưởng</t>
+          <t>Đã nhận phần thưởng rồi</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Nhận phần thưởng thất bại</t>
+          <t>Không thể nhận phần thưởng</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>ID Mùa không tồn tại</t>
+          <t>Mã mùa không tồn tại</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>ID Trận đấu không tồn tại</t>
+          <t>ID trận đấu không tồn tại</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Không thể lấy tỷ lệ Underdog Odds mới nhất</t>
+          <t>Không thể nhận Tỷ Lệ Thua Cuộc mới nhất</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Không thể xác định Underdog Odds</t>
+          <t>Không thể xác định Tỷ Lệ Thua</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Lỗi cấu hình tính toán Underdog Odds</t>
+          <t>Lỗi cấu hình tính toán Tỷ Lệ Thua</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Không thể lấy Underdog Odds</t>
+          <t>Không thể nhận Tỷ Lệ Thua Cuộc</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Đã đạt số lần Hỗ Trợ tối đa</t>
+          <t>Đã đạt số lần Hỗ trợ tối đa</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Không tìm thấy bản ghi Hỗ Trợ</t>
+          <t>Không tìm thấy lịch sử ủng hộ</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Lỗi hủy Hỗ Trợ</t>
+          <t>Lỗi hủy ủng hộ</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Hủy Hỗ Trợ thất bại</t>
+          <t>Hủy ủng hộ thất bại</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Không tìm thấy ID sự kiện</t>
+          <t>Không tìm thấy ID Sự kiện</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Insufficient Popularity</t>
+          <t>Độ nổi tiếng không đủ</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Không tìm thấy Vòng Bảng</t>
+          <t>Không tìm thấy Giai Đoạn Nhóm</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Không tìm thấy thông tin Vòng Bảng</t>
+          <t>Không tìm thấy thông tin Giai Đoạn Nhóm</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Insufficient Popularity</t>
+          <t>Độ nổi tiếng không đủ</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Lỗi tính toán Độ Phổ Biến</t>
+          <t>Lỗi tính toán độ nổi tiếng</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Lỗi thao tác Cube</t>
+          <t>Lỗi hành động Khối Lập Phương</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Không tìm thấy dữ liệu Vòng Bảng</t>
+          <t>Không tìm thấy dữ liệu Giai Đoạn Nhóm</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Lỗi loại thử thách</t>
+          <t>Lỗi loại thách đấu</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Không tìm thấy Cube</t>
+          <t>Không tìm thấy Khối Lập Phương</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Không tìm thấy Live Chat trận đấu</t>
+          <t>Không tìm thấy trận đấu Kênh Trò Chuyện Trực Tuyến</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Tin nhắn Live Chat không khớp với cuộc đua</t>
+          <t>Tin nhắn Kênh Trò Chuyện Trực Tuyến không khớp với chủng tộc</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Lỗi tin nhắn Live Chat</t>
+          <t>Lỗi tin nhắn Kênh Trò Chuyện Trực Tuyến</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Không tồn tại trận đấu của Live Chat</t>
+          <t>Trận đấu trong Live Chat không tồn tại</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Hiện không có thống kê Bảng Patron</t>
+          <t>Hiện không có số liệu Bảng Bảo Trợ</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Lấy thống kê Bảng Patron thất bại</t>
+          <t>Không lấy được số liệu Bảng Bảo Trợ</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Lỗi dữ liệu trận đấu hiện tại</t>
+          <t>Dữ liệu trận đấu hiện tại bị lỗi</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Lỗi thư mục hành động Khối</t>
+          <t>Lỗi thư mục hành động Khối Lập Phương</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Cấu hình Khối không tồn tại</t>
+          <t>Cấu hình Khối Lập Phương không tồn tại</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Mẫu Khối không tồn tại</t>
+          <t>Mẫu Khối Lập Phương không tồn tại</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Lỗi tạo Khối</t>
+          <t>Lỗi tạo Khối Lập Phương</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Không thể lấy Tỷ Lệ Underdog mới nhất</t>
+          <t>Không thể nhận Tỷ Lệ Thua Cuộc mới nhất</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Phần thưởng đã được nhận</t>
+          <t>Phần thưởng đã được nhận rồi</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Resonator đã được tuyển dụng</t>
+          <t>Resonator đã được tuyển</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Resonator đã được tuyển dụng</t>
+          <t>Resonator đã được tuyển</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Không còn lượt đặt lại</t>
+          <t>Đã hết lượt đặt lại</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương I Prologue của Nhiệm Vụ Chính để mở khóa Trượt</t>
+          <t>Tiến hành Chương Lời Mở Đầu Nhiệm Vụ Chính Chương I để mở khóa Lướt</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương II Act II của Nhiệm Vụ Chính để mở khóa Bay</t>
+          <t>Tiến hành Chương II Hồi II Nhiệm Vụ Chính để mở khóa Bay</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Download Resources</t>
+          <t>Tải Xuống Tài Nguyên</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Sự kiện không khả dụng</t>
+          <t>Sự kiện chưa khả dụng</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Không thể nhận phần thưởng vào lúc này</t>
+          <t>Hiện không thể nhận phần thưởng.</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Hiện không thể nhận phần thưởng</t>
+          <t>Hiện không thể nhận phần thưởng.</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Đã nhận phần thưởng</t>
+          <t>Đã nhận phần thưởng rồi</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Không tìm thấy phòng tiếp theo</t>
+          <t>Không tìm thấy phòng kế tiếp</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Chưa trang bị Cube</t>
+          <t>Chưa trang bị Khối Lập Phương</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Cube không khả dụng</t>
+          <t>Khối Lập Phương không khả dụng</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Cube đã được trang bị</t>
+          <t>Khối Lập Phương đã được trang bị</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Lỗi số lượng nhân vật</t>
+          <t>Lỗi số lượng diễn viên</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Phần thưởng không tồn tại</t>
+          <t>Thực thể phần thưởng không tồn tại</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Đã nhận phần thưởng</t>
+          <t>Đã nhận phần thưởng rồi</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Phần thưởng không tồn tại</t>
+          <t>Thực thể phần thưởng không tồn tại</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Cấu hình phần thưởng không tồn tại</t>
+          <t>Cấu hình thực thể phần thưởng không tồn tại</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Nhận phần thưởng thất bại</t>
+          <t>Phát thưởng thất bại</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Thử thách bị khóa</t>
+          <t>Thách đấu bị khóa</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Thử thách không có yêu cầu mở khóa</t>
+          <t>Thử thách không có yêu cầu mở khóa.</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Already Liked</t>
+          <t>Đã Thích</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Cube bị khóa</t>
+          <t>Khối Lập Phương đã bị khóa</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình phần thưởng Cube</t>
+          <t>Không tìm thấy cấu hình phần thưởng Khối Lập Phương</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình cấp độ Cube</t>
+          <t>Không tìm thấy cấu hình cấp độ Khối Lập Phương</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn tổng hợp</t>
+          <t>Đã đạt giới hạn Tổng hợp</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Không tìm thấy mô-đun vật phẩm</t>
+          <t>Không tìm thấy vật phẩm Mô-đun</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Vật phẩm đã bị khóa</t>
+          <t>Vật phẩm bị khóa</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình độ hiếm</t>
+          <t>Không tìm thấy cấu hình Độ Hiếm</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Vật phẩm tổng hợp đã được chọn</t>
+          <t>Vật phẩm Tổng hợp đã được chọn</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Chưa hoàn thành cấp độ trước</t>
+          <t>Cấp độ trước chưa hoàn thành</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình vị trí mô-đun</t>
+          <t>Không tìm thấy cấu hình vị trí Mô-đun</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Phó bản đã bị khóa</t>
+          <t>Hầm đã bị khóa</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Finalized</t>
+          <t>Đã Hoàn Thành</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Đã gửi yêu cầu</t>
+          <t>Đã gửi yêu cầu rồi</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Đã đạt số lượng yêu cầu tối đa</t>
+          <t>Số lượng yêu cầu đã đạt tối đa</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng yêu cầu thử thách</t>
+          <t>Chưa đáp ứng điều kiện thách đấu</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Đã thu thập phần thưởng</t>
+          <t>Đã thu thập hết vật phẩm rơi</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Electro Flare Challenge</t>
+          <t>Thử Thách Điện Quang</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 10</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 10</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 15</t>
+          <t>Mở khóa ở Cấp Độ Liên Minh 15</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Mở khóa ở Cấp Liên Minh 30</t>
+          <t>Mở khóa khi đạt Cấp Liên Minh 30</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Đã chọn Mô-đun Kỹ năng trùng lặp</t>
+          <t>Đã chọn Mô-đun Năng lực trùng lặp</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Đã triển khai thẻ tại vị trí này</t>
+          <t>Đã có thẻ được triển khai ở đó rồi</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Không thể quản lý bộ bài của đối thủ</t>
+          <t>Không thể kiểm soát bộ bài của đối thủ</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Đã nhận phần thưởng Resonator</t>
+          <t>Đã nhận thưởng Resonator</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Cấu hình Thử thách không tồn tại</t>
+          <t>Cấu hình thử thách không tồn tại</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Không thể thách đấu lại một trận đã kết thúc</t>
+          <t>Ngươi không thể thách đấu lại một trận đã kết thúc</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Đang trong questline đóng, không thể bật Chế độ Tập trung</t>
+          <t>Đang trong nhiệm vụ tuyến đóng, không thể kích hoạt Chế Độ Tập Trung</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Có</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Thách đấu ngay</t>
+          <t>Bắt Đầu Thử Thách</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Prepare More</t>
+          <t>Chế tạo thêm</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Nightmare Tacet Discords</t>
+          <t>Những Tacet Discord Ác Mộng</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Grim Nightmares</t>
+          <t>Ác Mộng U Minh</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Lọc để xem phần thưởng cho từng Giai đoạn</t>
+          <t>Lọc để xem phần thưởng cho từng Giai Đoạn</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>New Game</t>
+          <t>Trò Chơi Mới</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Nightmare Nest</t>
+          <t>Tổ Ác Mộng</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Nhận phần thưởng tiến độ thử thách không thành công</t>
+          <t>Không thể nhận phần thưởng tiến độ thử thách</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Hoàn thành Chương II Prologue Nhiệm vụ Chính để trải nghiệm trước</t>
+          <t>Hoàn thành Lời Mở Đầu Chương II trong Nhiệm Vụ Chính để trải nghiệm trước</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Hoàn thành "Test Run" để mở khóa</t>
+          <t>Hoàn thành "Chạy Thử" để mở khóa.</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Hoàn thành độ khó đầu tiên của "Celestial Stairway" để mở khóa</t>
+          <t>Hoàn thành độ khó đầu tiên của "Thiên Đàng Bậc Thang" để mở khóa</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Hoàn thành độ khó đầu tiên của "Whirling Rapids" để mở khóa</t>
+          <t>Hoàn thành độ khó đầu tiên của "Thác Nước Xoáy" để mở khóa</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Hoàn thành "Dream: Infinite I" để mở khóa</t>
+          <t>Hoàn thành "Giấc Mơ: Vô Tận I" để mở khóa</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Hoàn thành độ khó đầu tiên của "Barter Street" để mở khóa</t>
+          <t>Hoàn thành độ khó đầu tiên của "Phố Đổi Chác" để mở khóa</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Hoàn thành độ khó đầu tiên của "Scriptless Show" để mở khóa</t>
+          <t>Hoàn thành độ khó đầu tiên của "Vở Kịch Không Lời" để mở khóa</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Hoàn thành "Dream: Infinite II" để mở khóa</t>
+          <t>Hoàn thành "Giấc Mơ: Vô Tận II" để mở khóa</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Hoàn thành độ khó đầu tiên của "Sacrifice Night" để mở khóa</t>
+          <t>Hoàn thành độ khó đầu tiên của "Đêm Hy Sinh" để mở khóa</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Hoàn thành độ khó đầu tiên của "Mirror Maze" để mở khóa</t>
+          <t>Hoàn thành độ khó đầu tiên của "Mê Cung Gương" để mở khóa</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Hoàn thành "Dream: Infinite III" để mở khóa</t>
+          <t>Hoàn thành "Giấc Mơ: Vô Tận III" để mở khóa</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Mở khóa "Barter Street" để nhận</t>
+          <t>Mở khóa "Phố Trao Đổi" để nhận</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Mở khóa "Sacrifice Night" để nhận</t>
+          <t>Mở khóa "Đêm Hy Sinh" để nhận</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả độ khó của Stage trước để mở khóa</t>
+          <t>Hoàn thành tất cả độ khó của Giai Đoạn trước để mở khóa</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả độ khó của "Whirling Rapids" để mở khóa</t>
+          <t>Hoàn thành tất cả độ khó của "Thác Nước Xoáy" để mở khóa</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả độ khó của "Scriptless Show" để mở khóa</t>
+          <t>Hoàn thành tất cả độ khó của "Vở Diễn Không Kịch Bản" để mở khóa</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả độ khó của "Sacrifice Night" để mở khóa</t>
+          <t>Hoàn thành tất cả độ khó của "Đêm Hy Sinh" để mở khóa</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả độ khó của "Barter Street" để mở khóa</t>
+          <t>Hoàn thành tất cả độ khó của "Phố Đổi Chác" để mở khóa</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình thử thách</t>
+          <t>Không tìm thấy cấu hình thử thách.</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Thử thách không khả dụng</t>
+          <t>Thách đấu chưa mở</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Stage trước chưa được hoàn thành</t>
+          <t>Giai đoạn trước chưa được hoàn thành.</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Tên vượt quá giới hạn độ dài</t>
+          <t>Tên vượt quá giới hạn độ dài.</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
